--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D2">
         <v>132</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D3">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>
